--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post DFS_HRM-2031-0220/Panel-28/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post DFS_HRM-2031-0220/Panel-28/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -460,72 +460,72 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.43426</v>
+        <v>17.64838</v>
       </c>
       <c r="D2" t="n">
-        <v>17.42327</v>
+        <v>17.42075</v>
       </c>
       <c r="E2" t="n">
-        <v>17.74404</v>
+        <v>17.44878</v>
       </c>
       <c r="F2" t="n">
-        <v>44.5514</v>
+        <v>45.47937</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05154</v>
+        <v>0.05205</v>
       </c>
       <c r="H2" t="n">
-        <v>1.91782</v>
+        <v>1.92315</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.65521</v>
+        <v>17.59106</v>
       </c>
       <c r="D3" t="n">
-        <v>17.34971</v>
+        <v>17.31567</v>
       </c>
       <c r="E3" t="n">
-        <v>17.30695</v>
+        <v>17.34496</v>
       </c>
       <c r="F3" t="n">
-        <v>44.74706</v>
+        <v>43.89342</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05369</v>
+        <v>0.05348</v>
       </c>
       <c r="H3" t="n">
-        <v>1.91037</v>
+        <v>1.93128</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Unit 3</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.67917</v>
+        <v>17.67264</v>
       </c>
       <c r="D4" t="n">
-        <v>17.28364</v>
+        <v>17.43983</v>
       </c>
       <c r="E4" t="n">
-        <v>17.5857</v>
+        <v>17.53044</v>
       </c>
       <c r="F4" t="n">
-        <v>44.08393</v>
+        <v>43.73717</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05355</v>
+        <v>0.05255</v>
       </c>
       <c r="H4" t="n">
-        <v>1.88846</v>
+        <v>1.92765</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.57962</v>
+        <v>17.72664</v>
       </c>
       <c r="D5" t="n">
-        <v>17.31628</v>
+        <v>17.63716</v>
       </c>
       <c r="E5" t="n">
-        <v>17.53379</v>
+        <v>17.70797</v>
       </c>
       <c r="F5" t="n">
-        <v>44.79022</v>
+        <v>44.21926</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05267</v>
+        <v>0.05233</v>
       </c>
       <c r="H5" t="n">
-        <v>1.89459</v>
+        <v>1.92364</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.52483</v>
+        <v>17.84724</v>
       </c>
       <c r="D6" t="n">
-        <v>17.43075</v>
+        <v>17.21046</v>
       </c>
       <c r="E6" t="n">
-        <v>17.35055</v>
+        <v>17.46934</v>
       </c>
       <c r="F6" t="n">
-        <v>43.48788</v>
+        <v>44.22609</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0533</v>
+        <v>0.0541</v>
       </c>
       <c r="H6" t="n">
-        <v>1.91532</v>
+        <v>1.93266</v>
       </c>
     </row>
     <row r="7">
@@ -585,1922 +585,1611 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.58751</v>
+        <v>17.62657</v>
       </c>
       <c r="D7" t="n">
-        <v>17.29345</v>
+        <v>17.22612</v>
       </c>
       <c r="E7" t="n">
-        <v>17.35883</v>
+        <v>17.48028</v>
       </c>
       <c r="F7" t="n">
-        <v>45.1305</v>
+        <v>44.90447</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05317</v>
+        <v>0.05265</v>
       </c>
       <c r="H7" t="n">
-        <v>1.881</v>
+        <v>1.871</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unit 7</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.73981</v>
+        <v>17.41529</v>
       </c>
       <c r="D8" t="n">
-        <v>17.59325</v>
+        <v>17.22335</v>
       </c>
       <c r="E8" t="n">
-        <v>17.64641</v>
+        <v>17.24849</v>
       </c>
       <c r="F8" t="n">
-        <v>45.47156</v>
+        <v>44.26258</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05218</v>
+        <v>0.05363</v>
       </c>
       <c r="H8" t="n">
-        <v>1.89111</v>
+        <v>1.8885</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.95138</v>
+        <v>17.56997</v>
       </c>
       <c r="D9" t="n">
-        <v>17.42075</v>
+        <v>17.35361</v>
       </c>
       <c r="E9" t="n">
-        <v>17.45066</v>
+        <v>17.50358</v>
       </c>
       <c r="F9" t="n">
-        <v>43.97169</v>
+        <v>45.1635</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05194</v>
+        <v>0.05309</v>
       </c>
       <c r="H9" t="n">
-        <v>1.88216</v>
+        <v>1.91914</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.71838</v>
+        <v>17.93878</v>
       </c>
       <c r="D10" t="n">
-        <v>17.58883</v>
+        <v>17.41154</v>
       </c>
       <c r="E10" t="n">
-        <v>17.43445</v>
+        <v>17.5785</v>
       </c>
       <c r="F10" t="n">
-        <v>44.92137</v>
+        <v>44.18779</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05217</v>
+        <v>0.05356</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8904</v>
+        <v>1.92411</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Unit 10</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>17.51886</v>
-      </c>
-      <c r="D11" t="n">
-        <v>17.72391</v>
-      </c>
-      <c r="E11" t="n">
-        <v>17.34164</v>
-      </c>
-      <c r="F11" t="n">
-        <v>44.64676</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.05256</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.92915</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unit 11</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pad 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.63724</v>
+        <v>17.37819</v>
       </c>
       <c r="D12" t="n">
-        <v>17.55883</v>
+        <v>17.26876</v>
       </c>
       <c r="E12" t="n">
-        <v>17.59696</v>
+        <v>17.33232</v>
       </c>
       <c r="F12" t="n">
-        <v>45.77501</v>
+        <v>43.52951</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05291</v>
+        <v>0.053</v>
       </c>
       <c r="H12" t="n">
-        <v>1.91028</v>
+        <v>1.92446</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 12</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.60837</v>
+        <v>17.57233</v>
       </c>
       <c r="D13" t="n">
-        <v>17.32152</v>
+        <v>17.35851</v>
       </c>
       <c r="E13" t="n">
-        <v>17.25159</v>
+        <v>17.48681</v>
       </c>
       <c r="F13" t="n">
-        <v>44.10429</v>
+        <v>45.02007</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05331</v>
+        <v>0.05276</v>
       </c>
       <c r="H13" t="n">
-        <v>1.92344</v>
+        <v>1.85877</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 13</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17.51992</v>
+        <v>17.85375</v>
       </c>
       <c r="D14" t="n">
-        <v>17.37042</v>
+        <v>17.3723</v>
       </c>
       <c r="E14" t="n">
-        <v>17.82154</v>
+        <v>17.5777</v>
       </c>
       <c r="F14" t="n">
-        <v>44.09074</v>
+        <v>44.28374</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05217</v>
+        <v>0.05375</v>
       </c>
       <c r="H14" t="n">
-        <v>1.88939</v>
+        <v>1.8982</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 14</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.979</v>
+        <v>17.89342</v>
       </c>
       <c r="D15" t="n">
-        <v>17.02145</v>
+        <v>17.26148</v>
       </c>
       <c r="E15" t="n">
-        <v>17.50311</v>
+        <v>17.45551</v>
       </c>
       <c r="F15" t="n">
-        <v>45.08006</v>
+        <v>44.89331</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05364</v>
+        <v>0.05245</v>
       </c>
       <c r="H15" t="n">
-        <v>1.90067</v>
+        <v>1.92881</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 15</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.48088</v>
+        <v>17.63027</v>
       </c>
       <c r="D16" t="n">
-        <v>16.75955</v>
+        <v>17.5362</v>
       </c>
       <c r="E16" t="n">
-        <v>17.37894</v>
+        <v>17.53821</v>
       </c>
       <c r="F16" t="n">
-        <v>45.34996</v>
+        <v>44.41904</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05296</v>
+        <v>0.05361</v>
       </c>
       <c r="H16" t="n">
-        <v>1.89225</v>
+        <v>1.89547</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 16</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.63573</v>
+        <v>17.5092</v>
       </c>
       <c r="D17" t="n">
-        <v>17.67112</v>
+        <v>17.33821</v>
       </c>
       <c r="E17" t="n">
-        <v>17.68683</v>
+        <v>17.42324</v>
       </c>
       <c r="F17" t="n">
-        <v>44.04624</v>
+        <v>44.21702</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05213</v>
+        <v>0.05305</v>
       </c>
       <c r="H17" t="n">
-        <v>1.93689</v>
+        <v>1.90971</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 17</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.61988</v>
+        <v>17.59291</v>
       </c>
       <c r="D18" t="n">
-        <v>16.74579</v>
+        <v>17.24316</v>
       </c>
       <c r="E18" t="n">
-        <v>17.74658</v>
+        <v>17.4556</v>
       </c>
       <c r="F18" t="n">
-        <v>44.54362</v>
+        <v>44.82276</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05336</v>
+        <v>0.05375</v>
       </c>
       <c r="H18" t="n">
-        <v>1.87853</v>
+        <v>1.92303</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unit 18</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17.4841</v>
+        <v>17.77147</v>
       </c>
       <c r="D19" t="n">
-        <v>17.05966</v>
+        <v>17.33606</v>
       </c>
       <c r="E19" t="n">
-        <v>17.87736</v>
+        <v>17.43878</v>
       </c>
       <c r="F19" t="n">
-        <v>45.53254</v>
+        <v>44.55545</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05265</v>
+        <v>0.05302</v>
       </c>
       <c r="H19" t="n">
-        <v>1.9387</v>
+        <v>1.90187</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Unit 19</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.58143</v>
+        <v>17.68161</v>
       </c>
       <c r="D20" t="n">
-        <v>17.31396</v>
+        <v>17.37471</v>
       </c>
       <c r="E20" t="n">
-        <v>17.45117</v>
+        <v>17.52289</v>
       </c>
       <c r="F20" t="n">
-        <v>44.55805</v>
+        <v>44.60146</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05364</v>
+        <v>0.05255</v>
       </c>
       <c r="H20" t="n">
-        <v>1.93202</v>
+        <v>1.88828</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Unit 20</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>17.69363</v>
-      </c>
-      <c r="D21" t="n">
-        <v>17.52547</v>
-      </c>
-      <c r="E21" t="n">
-        <v>18.10645</v>
-      </c>
-      <c r="F21" t="n">
-        <v>43.93653</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.05412</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1.92176</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Unit 21</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SR Pad 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>17.35276</v>
+        <v>16.48726</v>
       </c>
       <c r="D22" t="n">
-        <v>17.4986</v>
+        <v>16.07811</v>
       </c>
       <c r="E22" t="n">
-        <v>17.71615</v>
+        <v>16.29821</v>
       </c>
       <c r="F22" t="n">
-        <v>44.54445</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.05303</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.91908</v>
+        <v>269.23314</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unit 22</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>17.48031</v>
+        <v>16.56933</v>
       </c>
       <c r="D23" t="n">
-        <v>17.39073</v>
+        <v>16.29579</v>
       </c>
       <c r="E23" t="n">
-        <v>17.38073</v>
+        <v>16.54876</v>
       </c>
       <c r="F23" t="n">
-        <v>44.62868</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.05238</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1.91715</v>
+        <v>265.69521</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Unit 23</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>17.42332</v>
+        <v>16.71878</v>
       </c>
       <c r="D24" t="n">
-        <v>17.21005</v>
+        <v>16.24942</v>
       </c>
       <c r="E24" t="n">
-        <v>17.65634</v>
+        <v>16.35055</v>
       </c>
       <c r="F24" t="n">
-        <v>44.63859</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.05284</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1.89637</v>
+        <v>268.9634</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unit 24</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>17.24706</v>
+        <v>16.72318</v>
       </c>
       <c r="D25" t="n">
-        <v>17.19204</v>
+        <v>16.2031</v>
       </c>
       <c r="E25" t="n">
-        <v>17.26453</v>
+        <v>16.33512</v>
       </c>
       <c r="F25" t="n">
-        <v>43.71499</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.05387</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1.87804</v>
+        <v>267.88133</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Unit 25</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>17.46849</v>
+        <v>16.56259</v>
       </c>
       <c r="D26" t="n">
-        <v>17.43113</v>
+        <v>16.099</v>
       </c>
       <c r="E26" t="n">
-        <v>17.8355</v>
+        <v>16.15278</v>
       </c>
       <c r="F26" t="n">
-        <v>43.8499</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.05311</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1.92841</v>
+        <v>262.44862</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unit 26</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>17.43231</v>
+        <v>16.35636</v>
       </c>
       <c r="D27" t="n">
-        <v>17.592</v>
+        <v>16.12922</v>
       </c>
       <c r="E27" t="n">
-        <v>17.26043</v>
+        <v>16.24639</v>
       </c>
       <c r="F27" t="n">
-        <v>44.44436</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.05365</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1.90942</v>
+        <v>265.83912</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unit 27</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>17.71609</v>
+        <v>16.56198</v>
       </c>
       <c r="D28" t="n">
-        <v>17.76527</v>
+        <v>16.23384</v>
       </c>
       <c r="E28" t="n">
-        <v>17.15842</v>
+        <v>16.45765</v>
       </c>
       <c r="F28" t="n">
-        <v>44.10858</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.05304</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1.88202</v>
+        <v>267.48244</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Unit 28</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>18.14803</v>
+        <v>16.37857</v>
       </c>
       <c r="D29" t="n">
-        <v>17.35207</v>
+        <v>16.23377</v>
       </c>
       <c r="E29" t="n">
-        <v>17.31122</v>
+        <v>16.33666</v>
       </c>
       <c r="F29" t="n">
-        <v>44.82245</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.05317</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1.90079</v>
+        <v>267.3432</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Unit 29</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>17.72986</v>
+        <v>16.50036</v>
       </c>
       <c r="D30" t="n">
-        <v>17.53658</v>
+        <v>16.2044</v>
       </c>
       <c r="E30" t="n">
-        <v>17.48047</v>
+        <v>16.29364</v>
       </c>
       <c r="F30" t="n">
-        <v>44.86352</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.05162</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1.88095</v>
+        <v>271.81817</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Unit 30</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>17.60746</v>
-      </c>
-      <c r="D31" t="n">
-        <v>17.30278</v>
-      </c>
-      <c r="E31" t="n">
-        <v>17.44225</v>
-      </c>
-      <c r="F31" t="n">
-        <v>43.89339</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.05159</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1.87476</v>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Unit 31</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>17.29085</v>
+        <v>17.71747</v>
       </c>
       <c r="D32" t="n">
-        <v>17.25082</v>
+        <v>16.75997</v>
       </c>
       <c r="E32" t="n">
-        <v>17.79886</v>
+        <v>17.1537</v>
       </c>
       <c r="F32" t="n">
-        <v>44.86365</v>
+        <v>23.08318</v>
       </c>
       <c r="G32" t="n">
-        <v>0.05307</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1.90181</v>
+        <v>35.54534</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Unit 32</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>17.50498</v>
+        <v>17.35626</v>
       </c>
       <c r="D33" t="n">
-        <v>16.97203</v>
+        <v>16.6118</v>
       </c>
       <c r="E33" t="n">
-        <v>17.30954</v>
+        <v>17.25408</v>
       </c>
       <c r="F33" t="n">
-        <v>44.51577</v>
+        <v>22.7579</v>
       </c>
       <c r="G33" t="n">
-        <v>0.05294</v>
-      </c>
-      <c r="H33" t="n">
-        <v>1.89504</v>
+        <v>35.80783</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Unit 33</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>17.53124</v>
+        <v>17.7252</v>
       </c>
       <c r="D34" t="n">
-        <v>17.68403</v>
+        <v>16.41963</v>
       </c>
       <c r="E34" t="n">
-        <v>17.25099</v>
+        <v>17.1621</v>
       </c>
       <c r="F34" t="n">
-        <v>45.18584</v>
+        <v>22.63912</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0524</v>
-      </c>
-      <c r="H34" t="n">
-        <v>1.90396</v>
+        <v>36.12433</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Unit 34</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>17.45839</v>
+        <v>17.58264</v>
       </c>
       <c r="D35" t="n">
-        <v>17.34584</v>
+        <v>16.77325</v>
       </c>
       <c r="E35" t="n">
-        <v>17.23947</v>
+        <v>17.12174</v>
       </c>
       <c r="F35" t="n">
-        <v>44.11409</v>
+        <v>22.94979</v>
       </c>
       <c r="G35" t="n">
-        <v>0.05376</v>
-      </c>
-      <c r="H35" t="n">
-        <v>1.88238</v>
+        <v>36.03299</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Unit 35</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>17.72381</v>
+        <v>17.4726</v>
       </c>
       <c r="D36" t="n">
-        <v>17.00783</v>
+        <v>16.88709</v>
       </c>
       <c r="E36" t="n">
-        <v>17.84307</v>
+        <v>17.3554</v>
       </c>
       <c r="F36" t="n">
-        <v>43.64652</v>
+        <v>22.74515</v>
       </c>
       <c r="G36" t="n">
-        <v>0.05304</v>
-      </c>
-      <c r="H36" t="n">
-        <v>1.96307</v>
+        <v>36.66772</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Unit 36</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>17.47145</v>
+        <v>17.32216</v>
       </c>
       <c r="D37" t="n">
-        <v>17.20963</v>
+        <v>16.77836</v>
       </c>
       <c r="E37" t="n">
-        <v>17.6714</v>
+        <v>17.17736</v>
       </c>
       <c r="F37" t="n">
-        <v>45.0809</v>
+        <v>22.64455</v>
       </c>
       <c r="G37" t="n">
-        <v>0.05299</v>
-      </c>
-      <c r="H37" t="n">
-        <v>1.84811</v>
+        <v>35.95537</v>
       </c>
     </row>
     <row r="38">
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Space</t>
-        </is>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>17.43554</v>
+      </c>
+      <c r="D38" t="n">
+        <v>16.58113</v>
+      </c>
+      <c r="E38" t="n">
+        <v>17.18641</v>
+      </c>
+      <c r="F38" t="n">
+        <v>22.69117</v>
+      </c>
+      <c r="G38" t="n">
+        <v>36.34984</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Trace 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>17.51868</v>
+        <v>17.24244</v>
       </c>
       <c r="D39" t="n">
-        <v>16.96629</v>
+        <v>16.37796</v>
       </c>
       <c r="E39" t="n">
-        <v>17.53258</v>
+        <v>16.99801</v>
       </c>
       <c r="F39" t="n">
-        <v>22.93857</v>
+        <v>22.63321</v>
       </c>
       <c r="G39" t="n">
-        <v>35.99206</v>
+        <v>35.38595</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>17.24875</v>
+        <v>17.35053</v>
       </c>
       <c r="D40" t="n">
-        <v>16.6942</v>
+        <v>16.83505</v>
       </c>
       <c r="E40" t="n">
-        <v>17.46304</v>
+        <v>16.83752</v>
       </c>
       <c r="F40" t="n">
-        <v>22.08791</v>
+        <v>22.82629</v>
       </c>
       <c r="G40" t="n">
-        <v>35.60998</v>
+        <v>36.70168</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>17.4568</v>
-      </c>
-      <c r="D41" t="n">
-        <v>17.24174</v>
-      </c>
-      <c r="E41" t="n">
-        <v>16.91595</v>
-      </c>
-      <c r="F41" t="n">
-        <v>23.02013</v>
-      </c>
-      <c r="G41" t="n">
-        <v>36.12764</v>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Trace 2</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>17.50717</v>
+        <v>17.2786</v>
       </c>
       <c r="D42" t="n">
-        <v>17.06547</v>
+        <v>16.55273</v>
       </c>
       <c r="E42" t="n">
-        <v>16.86686</v>
+        <v>17.25666</v>
       </c>
       <c r="F42" t="n">
-        <v>23.00068</v>
+        <v>22.68305</v>
       </c>
       <c r="G42" t="n">
-        <v>35.20593</v>
+        <v>35.62257</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>17.31541</v>
+        <v>17.2128</v>
       </c>
       <c r="D43" t="n">
-        <v>16.9384</v>
+        <v>16.68907</v>
       </c>
       <c r="E43" t="n">
-        <v>16.90143</v>
+        <v>17.11858</v>
       </c>
       <c r="F43" t="n">
-        <v>23.02955</v>
+        <v>22.69973</v>
       </c>
       <c r="G43" t="n">
-        <v>36.07944</v>
+        <v>36.21229</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>17.32953</v>
+        <v>17.47395</v>
       </c>
       <c r="D44" t="n">
-        <v>16.69526</v>
+        <v>16.90907</v>
       </c>
       <c r="E44" t="n">
-        <v>17.22699</v>
+        <v>17.208</v>
       </c>
       <c r="F44" t="n">
-        <v>22.96002</v>
+        <v>22.98988</v>
       </c>
       <c r="G44" t="n">
-        <v>36.00803</v>
+        <v>36.14057</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Unit 7</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>17.51027</v>
+        <v>17.49476</v>
       </c>
       <c r="D45" t="n">
-        <v>16.81092</v>
+        <v>16.70027</v>
       </c>
       <c r="E45" t="n">
-        <v>17.27017</v>
+        <v>17.32928</v>
       </c>
       <c r="F45" t="n">
-        <v>22.43386</v>
+        <v>22.69646</v>
       </c>
       <c r="G45" t="n">
-        <v>36.1903</v>
+        <v>35.20061</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>17.4414</v>
+        <v>17.85198</v>
       </c>
       <c r="D46" t="n">
-        <v>16.68867</v>
+        <v>16.41876</v>
       </c>
       <c r="E46" t="n">
-        <v>17.31707</v>
+        <v>17.46818</v>
       </c>
       <c r="F46" t="n">
-        <v>22.91731</v>
+        <v>22.15447</v>
       </c>
       <c r="G46" t="n">
-        <v>36.32968</v>
+        <v>36.02463</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>17.22692</v>
+        <v>17.28958</v>
       </c>
       <c r="D47" t="n">
-        <v>16.76454</v>
+        <v>17.01415</v>
       </c>
       <c r="E47" t="n">
-        <v>17.28434</v>
+        <v>17.09169</v>
       </c>
       <c r="F47" t="n">
-        <v>22.84685</v>
+        <v>22.84149</v>
       </c>
       <c r="G47" t="n">
-        <v>35.91507</v>
+        <v>36.3484</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Unit 10</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>17.22933</v>
+        <v>17.50234</v>
       </c>
       <c r="D48" t="n">
-        <v>16.80974</v>
+        <v>16.28617</v>
       </c>
       <c r="E48" t="n">
-        <v>17.07404</v>
+        <v>17.26041</v>
       </c>
       <c r="F48" t="n">
-        <v>22.54456</v>
+        <v>22.86668</v>
       </c>
       <c r="G48" t="n">
-        <v>35.89406</v>
+        <v>35.75733</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Unit 11</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>17.29187</v>
+        <v>17.39634</v>
       </c>
       <c r="D49" t="n">
-        <v>16.67636</v>
+        <v>16.83342</v>
       </c>
       <c r="E49" t="n">
-        <v>17.29374</v>
+        <v>17.30695</v>
       </c>
       <c r="F49" t="n">
-        <v>23.06245</v>
+        <v>22.81829</v>
       </c>
       <c r="G49" t="n">
-        <v>35.84272</v>
+        <v>35.99734</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Unit 12</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>17.39324</v>
+        <v>17.38903</v>
       </c>
       <c r="D50" t="n">
-        <v>16.94066</v>
+        <v>16.83964</v>
       </c>
       <c r="E50" t="n">
-        <v>16.92324</v>
+        <v>17.0038</v>
       </c>
       <c r="F50" t="n">
-        <v>22.31877</v>
+        <v>23.02627</v>
       </c>
       <c r="G50" t="n">
-        <v>35.22116</v>
+        <v>35.46101</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Unit 13</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>17.36046</v>
-      </c>
-      <c r="D51" t="n">
-        <v>16.47238</v>
-      </c>
-      <c r="E51" t="n">
-        <v>17.51668</v>
-      </c>
-      <c r="F51" t="n">
-        <v>23.353</v>
-      </c>
-      <c r="G51" t="n">
-        <v>35.9423</v>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Unit 14</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>via 1</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>17.54396</v>
+        <v>0.63541</v>
       </c>
       <c r="D52" t="n">
-        <v>16.88211</v>
-      </c>
-      <c r="E52" t="n">
-        <v>17.21074</v>
-      </c>
-      <c r="F52" t="n">
-        <v>22.66068</v>
-      </c>
-      <c r="G52" t="n">
-        <v>34.86959</v>
+        <v>1.16146</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Unit 15</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>17.66375</v>
+        <v>0.63759</v>
       </c>
       <c r="D53" t="n">
-        <v>17.17206</v>
-      </c>
-      <c r="E53" t="n">
-        <v>17.40304</v>
-      </c>
-      <c r="F53" t="n">
-        <v>23.17686</v>
-      </c>
-      <c r="G53" t="n">
-        <v>35.85108</v>
+        <v>1.17308</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Unit 16</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>17.78258</v>
+        <v>0.63208</v>
       </c>
       <c r="D54" t="n">
-        <v>16.97289</v>
-      </c>
-      <c r="E54" t="n">
-        <v>17.02527</v>
-      </c>
-      <c r="F54" t="n">
-        <v>22.59038</v>
-      </c>
-      <c r="G54" t="n">
-        <v>36.08345</v>
+        <v>1.15781</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Unit 17</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>17.54239</v>
+        <v>0.63343</v>
       </c>
       <c r="D55" t="n">
-        <v>16.61474</v>
-      </c>
-      <c r="E55" t="n">
-        <v>17.2862</v>
-      </c>
-      <c r="F55" t="n">
-        <v>22.21667</v>
-      </c>
-      <c r="G55" t="n">
-        <v>34.56058</v>
+        <v>1.16914</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Unit 18</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>17.2571</v>
+        <v>0.63093</v>
       </c>
       <c r="D56" t="n">
-        <v>16.79228</v>
-      </c>
-      <c r="E56" t="n">
-        <v>16.98704</v>
-      </c>
-      <c r="F56" t="n">
-        <v>22.44572</v>
-      </c>
-      <c r="G56" t="n">
-        <v>35.75538</v>
+        <v>1.13897</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Unit 19</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>17.28154</v>
+        <v>0.63955</v>
       </c>
       <c r="D57" t="n">
-        <v>16.79333</v>
-      </c>
-      <c r="E57" t="n">
-        <v>17.09706</v>
-      </c>
-      <c r="F57" t="n">
-        <v>23.29822</v>
-      </c>
-      <c r="G57" t="n">
-        <v>36.8272</v>
+        <v>1.17047</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Unit 20</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>17.34348</v>
+        <v>0.63569</v>
       </c>
       <c r="D58" t="n">
-        <v>16.80369</v>
-      </c>
-      <c r="E58" t="n">
-        <v>17.32122</v>
-      </c>
-      <c r="F58" t="n">
-        <v>22.81706</v>
-      </c>
-      <c r="G58" t="n">
-        <v>36.11283</v>
+        <v>1.15993</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Unit 21</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>17.61807</v>
+        <v>0.63123</v>
       </c>
       <c r="D59" t="n">
-        <v>16.82426</v>
-      </c>
-      <c r="E59" t="n">
-        <v>16.9647</v>
-      </c>
-      <c r="F59" t="n">
-        <v>23.03828</v>
-      </c>
-      <c r="G59" t="n">
-        <v>36.98958</v>
+        <v>1.18199</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Unit 22</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>17.94028</v>
+        <v>0.6380400000000001</v>
       </c>
       <c r="D60" t="n">
-        <v>16.77452</v>
-      </c>
-      <c r="E60" t="n">
-        <v>17.65506</v>
-      </c>
-      <c r="F60" t="n">
-        <v>22.47805</v>
-      </c>
-      <c r="G60" t="n">
-        <v>35.78989</v>
+        <v>1.1495</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Unit 23</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>17.6614</v>
-      </c>
-      <c r="D61" t="n">
-        <v>16.57498</v>
-      </c>
-      <c r="E61" t="n">
-        <v>17.34288</v>
-      </c>
-      <c r="F61" t="n">
-        <v>23.25476</v>
-      </c>
-      <c r="G61" t="n">
-        <v>36.30571</v>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Unit 24</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>via 2</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>17.38406</v>
+        <v>0.6412</v>
       </c>
       <c r="D62" t="n">
-        <v>16.84224</v>
-      </c>
-      <c r="E62" t="n">
-        <v>17.52842</v>
-      </c>
-      <c r="F62" t="n">
-        <v>22.65409</v>
-      </c>
-      <c r="G62" t="n">
-        <v>36.32063</v>
+        <v>1.18004</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Unit 25</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>17.44763</v>
+        <v>0.64169</v>
       </c>
       <c r="D63" t="n">
-        <v>16.73574</v>
-      </c>
-      <c r="E63" t="n">
-        <v>17.22078</v>
-      </c>
-      <c r="F63" t="n">
-        <v>22.40537</v>
-      </c>
-      <c r="G63" t="n">
-        <v>35.63652</v>
+        <v>1.19092</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Unit 26</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>17.48944</v>
+        <v>0.62612</v>
       </c>
       <c r="D64" t="n">
-        <v>17.1582</v>
-      </c>
-      <c r="E64" t="n">
-        <v>17.39658</v>
-      </c>
-      <c r="F64" t="n">
-        <v>22.5936</v>
-      </c>
-      <c r="G64" t="n">
-        <v>35.04966</v>
+        <v>1.15568</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Unit 27</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>17.90952</v>
+        <v>0.64885</v>
       </c>
       <c r="D65" t="n">
-        <v>16.48842</v>
-      </c>
-      <c r="E65" t="n">
-        <v>17.34382</v>
-      </c>
-      <c r="F65" t="n">
-        <v>22.9167</v>
-      </c>
-      <c r="G65" t="n">
-        <v>35.96419</v>
+        <v>1.16846</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Unit 28</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>17.253</v>
+        <v>0.63457</v>
       </c>
       <c r="D66" t="n">
-        <v>16.7649</v>
-      </c>
-      <c r="E66" t="n">
-        <v>17.17596</v>
-      </c>
-      <c r="F66" t="n">
-        <v>22.67644</v>
-      </c>
-      <c r="G66" t="n">
-        <v>36.64763</v>
+        <v>1.15164</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Unit 29</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>17.75231</v>
+        <v>0.62326</v>
       </c>
       <c r="D67" t="n">
-        <v>16.87397</v>
-      </c>
-      <c r="E67" t="n">
-        <v>17.13735</v>
-      </c>
-      <c r="F67" t="n">
-        <v>22.8252</v>
-      </c>
-      <c r="G67" t="n">
-        <v>36.04461</v>
+        <v>1.15021</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Unit 30</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>17.41779</v>
+        <v>0.64042</v>
       </c>
       <c r="D68" t="n">
-        <v>16.82519</v>
-      </c>
-      <c r="E68" t="n">
-        <v>16.95751</v>
-      </c>
-      <c r="F68" t="n">
-        <v>22.71308</v>
-      </c>
-      <c r="G68" t="n">
-        <v>36.00785</v>
+        <v>1.17974</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Unit 31</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>17.66932</v>
+        <v>0.63398</v>
       </c>
       <c r="D69" t="n">
-        <v>16.38997</v>
-      </c>
-      <c r="E69" t="n">
-        <v>17.09881</v>
-      </c>
-      <c r="F69" t="n">
-        <v>22.89766</v>
-      </c>
-      <c r="G69" t="n">
-        <v>35.66778</v>
+        <v>1.17651</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Unit 32</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>17.59394</v>
+        <v>0.62603</v>
       </c>
       <c r="D70" t="n">
-        <v>16.60886</v>
-      </c>
-      <c r="E70" t="n">
-        <v>17.12589</v>
-      </c>
-      <c r="F70" t="n">
-        <v>23.54778</v>
-      </c>
-      <c r="G70" t="n">
-        <v>36.04265</v>
+        <v>1.15524</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Unit 33</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>17.16842</v>
-      </c>
-      <c r="D71" t="n">
-        <v>17.04918</v>
-      </c>
-      <c r="E71" t="n">
-        <v>17.2844</v>
-      </c>
-      <c r="F71" t="n">
-        <v>22.91038</v>
-      </c>
-      <c r="G71" t="n">
-        <v>36.26856</v>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Unit 34</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>roughness</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>17.47617</v>
+        <v>0.78096</v>
       </c>
       <c r="D72" t="n">
-        <v>16.71914</v>
+        <v>0.08646</v>
       </c>
       <c r="E72" t="n">
-        <v>17.47581</v>
+        <v>0.63061</v>
       </c>
       <c r="F72" t="n">
-        <v>22.47963</v>
+        <v>1.00987</v>
       </c>
       <c r="G72" t="n">
-        <v>36.27894</v>
+        <v>0.11353</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.00804</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.09775</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.13383</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Unit 35</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>17.71422</v>
+        <v>0.7892</v>
       </c>
       <c r="D73" t="n">
-        <v>16.56127</v>
+        <v>0.08719</v>
       </c>
       <c r="E73" t="n">
-        <v>17.31069</v>
+        <v>0.63495</v>
       </c>
       <c r="F73" t="n">
-        <v>23.1561</v>
+        <v>1.0082</v>
       </c>
       <c r="G73" t="n">
-        <v>35.83997</v>
+        <v>0.11456</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.00792</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.09619</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.13126</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Unit 36</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>17.40196</v>
+        <v>0.78899</v>
       </c>
       <c r="D74" t="n">
-        <v>16.74547</v>
+        <v>0.08549</v>
       </c>
       <c r="E74" t="n">
-        <v>17.216</v>
+        <v>0.63325</v>
       </c>
       <c r="F74" t="n">
-        <v>22.42503</v>
+        <v>1.00621</v>
       </c>
       <c r="G74" t="n">
-        <v>34.31662</v>
+        <v>0.11665</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.00787</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.09599000000000001</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.13121</v>
       </c>
     </row>
     <row r="75">
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Rz mean</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Rz min</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>Ra max</t>
-        </is>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0.80147</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.08303000000000001</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.63648</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1.01967</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.11586</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.00792</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.09687999999999999</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.12774</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>roughness</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.79476</v>
+        <v>0.77942</v>
       </c>
       <c r="D76" t="n">
-        <v>0.08541</v>
+        <v>0.08638</v>
       </c>
       <c r="E76" t="n">
-        <v>0.6460900000000001</v>
+        <v>0.63552</v>
       </c>
       <c r="F76" t="n">
-        <v>1.0028</v>
+        <v>0.99869</v>
       </c>
       <c r="G76" t="n">
-        <v>0.11496</v>
+        <v>0.11474</v>
       </c>
       <c r="H76" t="n">
-        <v>0.008030000000000001</v>
+        <v>0.00808</v>
       </c>
       <c r="I76" t="n">
-        <v>0.09746</v>
+        <v>0.09862</v>
       </c>
       <c r="J76" t="n">
-        <v>0.13165</v>
+        <v>0.13109</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0.79522</v>
+        <v>0.77151</v>
       </c>
       <c r="D77" t="n">
-        <v>0.08604000000000001</v>
+        <v>0.08608</v>
       </c>
       <c r="E77" t="n">
-        <v>0.63096</v>
+        <v>0.63686</v>
       </c>
       <c r="F77" t="n">
-        <v>1.00703</v>
+        <v>0.9700299999999999</v>
       </c>
       <c r="G77" t="n">
-        <v>0.11464</v>
+        <v>0.11616</v>
       </c>
       <c r="H77" t="n">
-        <v>0.00779</v>
+        <v>0.00795</v>
       </c>
       <c r="I77" t="n">
-        <v>0.09877</v>
+        <v>0.09819</v>
       </c>
       <c r="J77" t="n">
-        <v>0.13082</v>
+        <v>0.13045</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.78821</v>
+        <v>0.77941</v>
       </c>
       <c r="D78" t="n">
-        <v>0.08573</v>
+        <v>0.08322</v>
       </c>
       <c r="E78" t="n">
-        <v>0.6248</v>
+        <v>0.6500899999999999</v>
       </c>
       <c r="F78" t="n">
-        <v>1.00669</v>
+        <v>1.0299</v>
       </c>
       <c r="G78" t="n">
-        <v>0.1137</v>
+        <v>0.11372</v>
       </c>
       <c r="H78" t="n">
-        <v>0.00801</v>
+        <v>0.00808</v>
       </c>
       <c r="I78" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.09744</v>
       </c>
       <c r="J78" t="n">
-        <v>0.13465</v>
+        <v>0.13197</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.77081</v>
+        <v>0.78266</v>
       </c>
       <c r="D79" t="n">
-        <v>0.08491</v>
+        <v>0.08487</v>
       </c>
       <c r="E79" t="n">
-        <v>0.63656</v>
+        <v>0.64368</v>
       </c>
       <c r="F79" t="n">
-        <v>0.99417</v>
+        <v>1.01967</v>
       </c>
       <c r="G79" t="n">
-        <v>0.11532</v>
+        <v>0.11512</v>
       </c>
       <c r="H79" t="n">
-        <v>0.00784</v>
+        <v>0.00801</v>
       </c>
       <c r="I79" t="n">
-        <v>0.09757</v>
+        <v>0.10096</v>
       </c>
       <c r="J79" t="n">
-        <v>0.13262</v>
+        <v>0.13076</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.78667</v>
+        <v>0.80102</v>
       </c>
       <c r="D80" t="n">
-        <v>0.08648</v>
+        <v>0.08541</v>
       </c>
       <c r="E80" t="n">
-        <v>0.63629</v>
+        <v>0.62721</v>
       </c>
       <c r="F80" t="n">
-        <v>1.00471</v>
+        <v>1.01364</v>
       </c>
       <c r="G80" t="n">
-        <v>0.11494</v>
+        <v>0.11596</v>
       </c>
       <c r="H80" t="n">
-        <v>0.00805</v>
+        <v>0.00795</v>
       </c>
       <c r="I80" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.09757</v>
       </c>
       <c r="J80" t="n">
-        <v>0.13209</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>0.79592</v>
-      </c>
-      <c r="D81" t="n">
-        <v>0.08527999999999999</v>
-      </c>
-      <c r="E81" t="n">
-        <v>0.642</v>
-      </c>
-      <c r="F81" t="n">
-        <v>1.0023</v>
-      </c>
-      <c r="G81" t="n">
-        <v>0.11329</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0.008070000000000001</v>
-      </c>
-      <c r="I81" t="n">
-        <v>0.09848</v>
-      </c>
-      <c r="J81" t="n">
-        <v>0.1332</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>0.77494</v>
-      </c>
-      <c r="D82" t="n">
-        <v>0.08396000000000001</v>
-      </c>
-      <c r="E82" t="n">
-        <v>0.63387</v>
-      </c>
-      <c r="F82" t="n">
-        <v>1.01121</v>
-      </c>
-      <c r="G82" t="n">
-        <v>0.1136</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0.00792</v>
-      </c>
-      <c r="I82" t="n">
-        <v>0.09836</v>
-      </c>
-      <c r="J82" t="n">
-        <v>0.13246</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>0.7878500000000001</v>
-      </c>
-      <c r="D83" t="n">
-        <v>0.08525000000000001</v>
-      </c>
-      <c r="E83" t="n">
-        <v>0.62959</v>
-      </c>
-      <c r="F83" t="n">
-        <v>1.01677</v>
-      </c>
-      <c r="G83" t="n">
-        <v>0.11345</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0.00809</v>
-      </c>
-      <c r="I83" t="n">
-        <v>0.0982</v>
-      </c>
-      <c r="J83" t="n">
-        <v>0.13207</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>0.78656</v>
-      </c>
-      <c r="D84" t="n">
-        <v>0.08552999999999999</v>
-      </c>
-      <c r="E84" t="n">
-        <v>0.63697</v>
-      </c>
-      <c r="F84" t="n">
-        <v>1.0078</v>
-      </c>
-      <c r="G84" t="n">
-        <v>0.11628</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0.00814</v>
-      </c>
-      <c r="I84" t="n">
-        <v>0.09685000000000001</v>
-      </c>
-      <c r="J84" t="n">
-        <v>0.13623</v>
+        <v>0.13327</v>
       </c>
     </row>
   </sheetData>
